--- a/tumores/2. Nasofaringe.xlsx
+++ b/tumores/2. Nasofaringe.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\Proyecto Practicas\tumores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB285092-56B4-4D99-9765-80EF358B7B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD442E7-F1B6-44A5-8611-551AB2594F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="91">
   <si>
     <t>T</t>
   </si>
@@ -140,21 +140,6 @@
   </si>
   <si>
     <t>&lt;3 áreas</t>
-  </si>
-  <si>
-    <t>Debajo del cricoides</t>
-  </si>
-  <si>
-    <t>Hipofaringe</t>
-  </si>
-  <si>
-    <t>Órbita</t>
-  </si>
-  <si>
-    <t>Nervios craneales</t>
-  </si>
-  <si>
-    <t>Glandula paratiroidea</t>
   </si>
   <si>
     <t>T1, T2</t>
@@ -293,30 +278,9 @@
     <t>M0: Sin metástasis a distancia</t>
   </si>
   <si>
-    <t>M1a: Metástasis pero no más de 3 áreas afectadas</t>
-  </si>
-  <si>
     <t>M1b: Metástasis con más de 3 áreas afectadas</t>
   </si>
   <si>
-    <t>M.Unilateral cervical &lt;6cm</t>
-  </si>
-  <si>
-    <t>M.Unilateral retrofaringea &lt;6cm, encima del cricoides</t>
-  </si>
-  <si>
-    <t>M.Bilateral retrofaringea &lt;6cm, encima del cricoides</t>
-  </si>
-  <si>
-    <t>M.Unilateral cervical &lt;6cm, encima del cricoides</t>
-  </si>
-  <si>
-    <t>M.Unilateral cervical &gt;6cm</t>
-  </si>
-  <si>
-    <t>M.Bilateral cervical &gt;6cm</t>
-  </si>
-  <si>
     <t>No identificado, VEB+</t>
   </si>
   <si>
@@ -339,6 +303,48 @@
   </si>
   <si>
     <t>Uno, Varios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compromiso de : </t>
+  </si>
+  <si>
+    <t>Infiltración  :</t>
+  </si>
+  <si>
+    <t>Compromiso Nervios craneales</t>
+  </si>
+  <si>
+    <t>Compromiso Hipofaringe</t>
+  </si>
+  <si>
+    <t>Compromiso Órbita</t>
+  </si>
+  <si>
+    <t>Compromiso Glandula paratiroidea</t>
+  </si>
+  <si>
+    <t>M.Unilateral G.cervicales &lt;6cm</t>
+  </si>
+  <si>
+    <t>M.Unilateral G.cervicales &gt;6cm</t>
+  </si>
+  <si>
+    <t>M.Bilateral G.cervicales &gt;6cm</t>
+  </si>
+  <si>
+    <t>M1a: Metástasis con menos de 3 áreas afectadas</t>
+  </si>
+  <si>
+    <t>Disem. Debajo del borde inferior del cricoides</t>
+  </si>
+  <si>
+    <t>M.Unilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides</t>
+  </si>
+  <si>
+    <t>M.Bilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides</t>
+  </si>
+  <si>
+    <t>M.Unilateral G.cervicales &lt;6cm, encima del  borde inferior del cricoides</t>
   </si>
 </sst>
 </file>
@@ -926,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -941,14 +947,14 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -956,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -971,14 +977,14 @@
         <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -986,14 +992,14 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1001,14 +1007,14 @@
         <v>0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1016,14 +1022,14 @@
         <v>0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1031,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -1039,14 +1045,16 @@
       <c r="D9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>30</v>
@@ -1054,21 +1062,23 @@
       <c r="D10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1076,14 +1086,14 @@
         <v>0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1091,14 +1101,14 @@
         <v>0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1106,14 +1116,14 @@
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1121,14 +1131,14 @@
         <v>0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1136,14 +1146,14 @@
         <v>0</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1151,7 +1161,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>13</v>
@@ -1165,7 +1175,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
@@ -1179,16 +1189,16 @@
         <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -1196,16 +1206,16 @@
         <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -1213,16 +1223,16 @@
         <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -1230,16 +1240,16 @@
         <v>12</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1247,13 +1257,13 @@
         <v>12</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -1261,13 +1271,13 @@
         <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1275,14 +1285,14 @@
         <v>12</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1290,7 +1300,7 @@
         <v>18</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>19</v>
@@ -1304,13 +1314,13 @@
         <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1318,13 +1328,13 @@
         <v>18</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1372,7 +1382,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>14</v>
@@ -1381,12 +1391,12 @@
         <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -1395,12 +1405,12 @@
         <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>32</v>
@@ -1417,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>19</v>

--- a/tumores/2. Nasofaringe.xlsx
+++ b/tumores/2. Nasofaringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD442E7-F1B6-44A5-8611-551AB2594F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDA49A7-5E99-49ED-9C29-F84775251B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -323,9 +323,6 @@
     <t>Compromiso Glandula paratiroidea</t>
   </si>
   <si>
-    <t>M.Unilateral G.cervicales &lt;6cm</t>
-  </si>
-  <si>
     <t>M.Unilateral G.cervicales &gt;6cm</t>
   </si>
   <si>
@@ -338,13 +335,16 @@
     <t>Disem. Debajo del borde inferior del cricoides</t>
   </si>
   <si>
-    <t>M.Unilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides</t>
-  </si>
-  <si>
-    <t>M.Bilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides</t>
-  </si>
-  <si>
-    <t>M.Unilateral G.cervicales &lt;6cm, encima del  borde inferior del cricoides</t>
+    <t xml:space="preserve">M.Unilateral G.cervicales &lt;6cm. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.Unilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.Bilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.Unilateral G.cervicales &lt;6cm, encima del  borde inferior del cricoides. </t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1198,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -1263,7 +1263,7 @@
         <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -1277,7 +1277,7 @@
         <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1292,7 +1292,7 @@
         <v>33</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1314,7 +1314,7 @@
         <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>34</v>

--- a/tumores/2. Nasofaringe.xlsx
+++ b/tumores/2. Nasofaringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDA49A7-5E99-49ED-9C29-F84775251B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE69414-BAF3-46BF-AAA6-11F915EE19F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>

--- a/tumores/2. Nasofaringe.xlsx
+++ b/tumores/2. Nasofaringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE69414-BAF3-46BF-AAA6-11F915EE19F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F64303D-166A-4049-B8A6-2CDE03A6ECE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
